--- a/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBarNegative.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/ConditionalFormatting/CFDataBarNegative.xlsx
@@ -408,7 +408,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b83d7c8-0c36-43bc-bd2e-b4f957032858}</x14:id>
+          <x14:id>{a152be9c-1707-42ed-91dd-e655838d7073}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -422,7 +422,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b85a964b-61fa-4075-b2a4-57373086d521}</x14:id>
+          <x14:id>{fc20990d-2005-49cc-95f3-1a00883b9dc5}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -436,7 +436,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b83d7c8-0c36-43bc-bd2e-b4f957032858}">
+          <x14:cfRule type="dataBar" id="{a152be9c-1707-42ed-91dd-e655838d7073}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -451,7 +451,7 @@
           <xm:sqref>A1:A4</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b85a964b-61fa-4075-b2a4-57373086d521}">
+          <x14:cfRule type="dataBar" id="{fc20990d-2005-49cc-95f3-1a00883b9dc5}">
             <x14:dataBar minLength="0" maxLength="100" showValue="0" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>-100</xm:f>
